--- a/gan/result/color1.xlsx
+++ b/gan/result/color1.xlsx
@@ -4,13 +4,16 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255" firstSheet="1"/>
+    <workbookView windowWidth="28800" windowHeight="12255" firstSheet="1" activeTab="6"/>
   </bookViews>
   <sheets>
-    <sheet name="SAGE_100k_domain10" sheetId="1" r:id="rId1"/>
-    <sheet name="domain15" sheetId="3" r:id="rId2"/>
-    <sheet name="bays" sheetId="2" r:id="rId3"/>
+    <sheet name="bays" sheetId="2" r:id="rId1"/>
+    <sheet name="SAGE_100k_domain10" sheetId="1" r:id="rId2"/>
+    <sheet name="domain15" sheetId="3" r:id="rId3"/>
     <sheet name="domain20" sheetId="4" r:id="rId4"/>
+    <sheet name="domain10_weight" sheetId="5" r:id="rId5"/>
+    <sheet name="domian15_weight" sheetId="6" r:id="rId6"/>
+    <sheet name="domain20_weight" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="71">
   <si>
     <t>TV</t>
   </si>
@@ -116,6 +119,9 @@
     <t>0.7019333243370056</t>
   </si>
   <si>
+    <t>0.5004500150680542</t>
+  </si>
+  <si>
     <t>0.7964166402816772</t>
   </si>
   <si>
@@ -126,19 +132,150 @@
   </si>
   <si>
     <t>0.9466500282287598</t>
+  </si>
+  <si>
+    <t>0.6661333441734314</t>
+  </si>
+  <si>
+    <t>domain</t>
+  </si>
+  <si>
+    <t>tv</t>
+  </si>
+  <si>
+    <t>real_tv</t>
+  </si>
+  <si>
+    <t>weight</t>
+  </si>
+  <si>
+    <t>loc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10
+</t>
+  </si>
+  <si>
+    <t>0.1</t>
+  </si>
+  <si>
+    <t>0.0992284907574253</t>
+  </si>
+  <si>
+    <t>1.4</t>
+  </si>
+  <si>
+    <t>1.5</t>
+  </si>
+  <si>
+    <t>0.193577918009981</t>
+  </si>
+  <si>
+    <t>1.7</t>
+  </si>
+  <si>
+    <t>2.0</t>
+  </si>
+  <si>
+    <t>0.294150774673965</t>
+  </si>
+  <si>
+    <t>1.3</t>
+  </si>
+  <si>
+    <t>1.6</t>
+  </si>
+  <si>
+    <t>0.395792593920223</t>
+  </si>
+  <si>
+    <t>1.9</t>
+  </si>
+  <si>
+    <t>0.500265302120678</t>
+  </si>
+  <si>
+    <t>0.9</t>
+  </si>
+  <si>
+    <t>1.2</t>
+  </si>
+  <si>
+    <t>0.594199197189847</t>
+  </si>
+  <si>
+    <t>0.69316732774041</t>
+  </si>
+  <si>
+    <t>1.0</t>
+  </si>
+  <si>
+    <t>0.803669455706338</t>
+  </si>
+  <si>
+    <t>0.893178025255485</t>
+  </si>
+  <si>
+    <t>0.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15
+</t>
+  </si>
+  <si>
+    <t>0.0995387443236106</t>
+  </si>
+  <si>
+    <t>0.199867971152775</t>
+  </si>
+  <si>
+    <t>0.300217343752401</t>
+  </si>
+  <si>
+    <t>0.399890533604606</t>
+  </si>
+  <si>
+    <t>0.500629463866624</t>
+  </si>
+  <si>
+    <t>0.598508688336019</t>
+  </si>
+  <si>
+    <t>0.700196311434368</t>
+  </si>
+  <si>
+    <t>0.800334454296785</t>
+  </si>
+  <si>
+    <t>0.899478838891871</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="23">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -491,12 +628,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -632,150 +784,160 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1301,143 +1463,108 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
+  <dimension ref="A1:B12"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="17.375" customWidth="1"/>
-    <col min="2" max="2" width="19.75" customWidth="1"/>
+    <col min="2" max="2" width="21" customWidth="1"/>
+    <col min="3" max="3" width="26" customWidth="1"/>
+    <col min="4" max="4" width="13.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" ht="14.25" spans="1:2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="4">
+    </row>
+    <row r="2" ht="14.25" spans="1:2">
+      <c r="A2" s="10">
         <v>0</v>
       </c>
-      <c r="B2" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2">
-        <v>2187</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="5">
-        <v>0.0992284907574253</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3">
-        <v>4375</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="5">
-        <v>0.193577918009981</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4">
-        <v>30631</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="5">
-        <v>0.294150774673965</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5">
-        <v>12033</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="5">
-        <v>0.395792593920223</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6">
-        <v>25161</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="5">
-        <v>0.500265302120678</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7">
-        <v>17503</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="5">
-        <v>0.594199197189847</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8">
-        <v>27349</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="5">
-        <v>0.69316732774041</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9">
-        <v>27349</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="5">
-        <v>0.803669455706338</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10">
-        <v>17503</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="5">
-        <v>0.893178025255485</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11">
-        <v>24067</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="4">
+      <c r="B2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="3" ht="14.25" spans="1:2">
+      <c r="A3" s="10">
+        <v>0.1</v>
+      </c>
+      <c r="B3">
+        <v>0.55</v>
+      </c>
+    </row>
+    <row r="4" ht="14.25" spans="1:2">
+      <c r="A4" s="10">
+        <v>0.2</v>
+      </c>
+      <c r="B4">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="5" ht="14.25" spans="1:2">
+      <c r="A5" s="10">
+        <v>0.3</v>
+      </c>
+      <c r="B5">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="6" ht="14.25" spans="1:2">
+      <c r="A6" s="10">
+        <v>0.4</v>
+      </c>
+      <c r="B6">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="7" ht="14.25" spans="1:2">
+      <c r="A7" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="B7">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="8" ht="14.25" spans="1:2">
+      <c r="A8" s="10">
+        <v>0.6</v>
+      </c>
+      <c r="B8">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="9" ht="14.25" spans="1:2">
+      <c r="A9" s="10">
+        <v>0.7</v>
+      </c>
+      <c r="B9">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="10" ht="14.25" spans="1:2">
+      <c r="A10" s="10">
+        <v>0.8</v>
+      </c>
+      <c r="B10">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="11" ht="14.25" spans="1:2">
+      <c r="A11" s="10">
+        <v>0.9</v>
+      </c>
+      <c r="B11">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="12" ht="14.25" spans="1:2">
+      <c r="A12" s="10">
         <v>1</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C12">
-        <v>15315</v>
+      <c r="B12">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1452,8 +1579,8 @@
   <dimension ref="A1:C12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="18.375" customWidth="1"/>
-    <col min="2" max="2" width="20.75" customWidth="1"/>
+    <col min="1" max="1" width="17.375" customWidth="1"/>
+    <col min="2" max="2" width="19.75" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1468,10 +1595,10 @@
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="4">
+      <c r="A2" s="8">
         <v>0</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="11" t="s">
         <v>3</v>
       </c>
       <c r="C2">
@@ -1479,113 +1606,113 @@
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="5">
-        <v>0.0995387443236106</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>14</v>
+      <c r="A3" s="9">
+        <v>0.0992284907574253</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>4</v>
       </c>
       <c r="C3">
         <v>4375</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="5">
-        <v>0.199867971152775</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>15</v>
+      <c r="A4" s="9">
+        <v>0.193577918009981</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>5</v>
       </c>
       <c r="C4">
-        <v>28443</v>
+        <v>30631</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="5">
-        <v>0.300217343752401</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>16</v>
+      <c r="A5" s="9">
+        <v>0.294150774673965</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>6</v>
       </c>
       <c r="C5">
+        <v>12033</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="9">
+        <v>0.395792593920223</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6">
         <v>25161</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="5">
-        <v>0.399890533604606</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6">
-        <v>36101</v>
-      </c>
-    </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="5">
-        <v>0.500629463866624</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>18</v>
+      <c r="A7" s="9">
+        <v>0.500265302120678</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>8</v>
       </c>
       <c r="C7">
         <v>17503</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="5">
-        <v>0.598508688336019</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>19</v>
+      <c r="A8" s="9">
+        <v>0.594199197189847</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>9</v>
       </c>
       <c r="C8">
-        <v>21879</v>
+        <v>27349</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="5">
-        <v>0.700196311434368</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>20</v>
+      <c r="A9" s="9">
+        <v>0.69316732774041</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>10</v>
       </c>
       <c r="C9">
-        <v>19691</v>
+        <v>27349</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="5">
-        <v>0.800334454296785</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>21</v>
+      <c r="A10" s="9">
+        <v>0.803669455706338</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>11</v>
       </c>
       <c r="C10">
-        <v>21879</v>
+        <v>17503</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="5">
-        <v>0.899478838891871</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>22</v>
+      <c r="A11" s="9">
+        <v>0.893178025255485</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>12</v>
       </c>
       <c r="C11">
-        <v>37195</v>
+        <v>24067</v>
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="4">
+      <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="11" t="s">
         <v>13</v>
       </c>
       <c r="C12">
-        <v>6563</v>
+        <v>15315</v>
       </c>
     </row>
   </sheetData>
@@ -1597,108 +1724,143 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
   <cols>
-    <col min="2" max="2" width="21" customWidth="1"/>
-    <col min="3" max="3" width="26" customWidth="1"/>
-    <col min="4" max="4" width="13.125" customWidth="1"/>
+    <col min="1" max="1" width="18.375" customWidth="1"/>
+    <col min="2" max="2" width="20.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" spans="1:2">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" ht="14.25" spans="1:2">
-      <c r="A2" s="3">
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="8">
         <v>0</v>
       </c>
-      <c r="B2">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="3" ht="14.25" spans="1:2">
-      <c r="A3" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="B3">
-        <v>0.55</v>
-      </c>
-    </row>
-    <row r="4" ht="14.25" spans="1:2">
-      <c r="A4" s="3">
-        <v>0.2</v>
-      </c>
-      <c r="B4">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="5" ht="14.25" spans="1:2">
-      <c r="A5" s="3">
-        <v>0.3</v>
-      </c>
-      <c r="B5">
-        <v>0.65</v>
-      </c>
-    </row>
-    <row r="6" ht="14.25" spans="1:2">
-      <c r="A6" s="3">
-        <v>0.4</v>
-      </c>
-      <c r="B6">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="7" ht="14.25" spans="1:2">
-      <c r="A7" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="B7">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="8" ht="14.25" spans="1:2">
-      <c r="A8" s="3">
-        <v>0.6</v>
-      </c>
-      <c r="B8">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="9" ht="14.25" spans="1:2">
-      <c r="A9" s="3">
-        <v>0.7</v>
-      </c>
-      <c r="B9">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="10" ht="14.25" spans="1:2">
-      <c r="A10" s="3">
-        <v>0.8</v>
-      </c>
-      <c r="B10">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="11" ht="14.25" spans="1:2">
-      <c r="A11" s="3">
-        <v>0.9</v>
-      </c>
-      <c r="B11">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="12" ht="14.25" spans="1:2">
-      <c r="A12" s="3">
+      <c r="B2" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2">
+        <v>2187</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="9">
+        <v>0.0995387443236106</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3">
+        <v>4375</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="9">
+        <v>0.199867971152775</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4">
+        <v>28443</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="9">
+        <v>0.300217343752401</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5">
+        <v>25161</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="9">
+        <v>0.399890533604606</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6">
+        <v>36101</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="9">
+        <v>0.500629463866624</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7">
+        <v>17503</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="9">
+        <v>0.598508688336019</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8">
+        <v>21879</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="9">
+        <v>0.700196311434368</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9">
+        <v>19691</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="9">
+        <v>0.800334454296785</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10">
+        <v>21879</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="9">
+        <v>0.899478838891871</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11">
+        <v>37195</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12">
-        <v>1</v>
+      <c r="B12" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12">
+        <v>6563</v>
       </c>
     </row>
   </sheetData>
@@ -1730,10 +1892,10 @@
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="1">
+      <c r="A2" s="6">
         <v>0</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="11" t="s">
         <v>23</v>
       </c>
       <c r="C2">
@@ -1741,10 +1903,10 @@
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="2">
+      <c r="A3" s="7">
         <v>0.101143207694175</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="11" t="s">
         <v>24</v>
       </c>
       <c r="C3">
@@ -1752,10 +1914,10 @@
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="1">
+      <c r="A4" s="6">
         <v>0.200154924981712</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="11" t="s">
         <v>25</v>
       </c>
       <c r="C4">
@@ -1763,10 +1925,10 @@
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="1">
+      <c r="A5" s="6">
         <v>0.299338977674621</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="11" t="s">
         <v>26</v>
       </c>
       <c r="C5">
@@ -1774,10 +1936,10 @@
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="1">
+      <c r="A6" s="6">
         <v>0.400678189503125</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="11" t="s">
         <v>27</v>
       </c>
       <c r="C6">
@@ -1785,63 +1947,1278 @@
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="1">
+      <c r="A7" s="6">
         <v>0.499870089058159</v>
       </c>
+      <c r="B7" s="11" t="s">
+        <v>28</v>
+      </c>
       <c r="C7">
-        <v>17503</v>
+        <v>12033</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="1">
+      <c r="A8" s="6">
         <v>0.599933246714468</v>
       </c>
-      <c r="B8" s="6" t="s">
-        <v>28</v>
+      <c r="B8" s="11" t="s">
+        <v>29</v>
       </c>
       <c r="C8">
         <v>14221</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="1">
+      <c r="A9" s="6">
         <v>0.700221096835872</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>29</v>
+      <c r="B9" s="11" t="s">
+        <v>30</v>
       </c>
       <c r="C9">
         <v>18597</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="1">
+      <c r="A10" s="6">
         <v>0.800435412423209</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>30</v>
+      <c r="B10" s="11" t="s">
+        <v>31</v>
       </c>
       <c r="C10">
         <v>25161</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="1">
+      <c r="A11" s="6">
         <v>0.900007855569501</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>31</v>
+      <c r="B11" s="11" t="s">
+        <v>32</v>
       </c>
       <c r="C11">
         <v>24067</v>
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="1">
+      <c r="A12" s="6">
         <v>1</v>
       </c>
+      <c r="B12" s="11" t="s">
+        <v>33</v>
+      </c>
       <c r="C12">
-        <v>6563</v>
+        <v>1093</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B2" s="4">
+        <v>0</v>
+      </c>
+      <c r="C2" s="4">
+        <v>0</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E2" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E3" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E4" s="4">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E5" s="4">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E6" s="4">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E7" s="4">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B8" s="4">
+        <v>0.3</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E8" s="4">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="4">
+        <v>0.3</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E9" s="4">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="4">
+        <v>0.4</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E10" s="4">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B11" s="4">
+        <v>0.4</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E11" s="4">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E12" s="4">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E13" s="4">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E14" s="4">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E15" s="4">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E16" s="4">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E17" s="4">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="4">
+        <v>0.8</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E18" s="4">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="4">
+        <v>0.8</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E19" s="4">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B20" s="4">
+        <v>0.9</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E20" s="4">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" s="4">
+        <v>0.9</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E21" s="4">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B22" s="4">
+        <v>1</v>
+      </c>
+      <c r="C22" s="4">
+        <v>1</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E22" s="4">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B23" s="4">
+        <v>1</v>
+      </c>
+      <c r="C23" s="4">
+        <v>1</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E23" s="4">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B2" s="4">
+        <v>0</v>
+      </c>
+      <c r="C2" s="4">
+        <v>0</v>
+      </c>
+      <c r="D2" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="E2" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="E3" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="D4" s="4">
+        <v>2.75</v>
+      </c>
+      <c r="E4" s="4">
+        <v>3298</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="D5" s="4">
+        <v>2.95</v>
+      </c>
+      <c r="E5" s="4">
+        <v>3298</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B6" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="D6" s="4">
+        <v>1.15</v>
+      </c>
+      <c r="E6" s="4">
+        <v>1344</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B7" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="D7" s="4">
+        <v>1.25</v>
+      </c>
+      <c r="E7" s="4">
+        <v>1344</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B8" s="4">
+        <v>0.3</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="D8" s="4">
+        <v>2.15</v>
+      </c>
+      <c r="E8" s="4">
+        <v>2571</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="4">
+        <v>0.3</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="D9" s="5">
+        <v>2.6</v>
+      </c>
+      <c r="E9" s="4">
+        <v>2571</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B10" s="4">
+        <v>0.4</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="D10" s="4">
+        <v>1.85</v>
+      </c>
+      <c r="E10" s="4">
+        <v>2206</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B11" s="4">
+        <v>0.4</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="D11" s="4">
+        <v>2.35</v>
+      </c>
+      <c r="E11" s="4">
+        <v>2206</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B12" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="D12" s="5">
+        <v>1.8</v>
+      </c>
+      <c r="E12" s="4">
+        <v>2148</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B13" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="D13" s="4">
+        <v>2.45</v>
+      </c>
+      <c r="E13" s="4">
+        <v>2148</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B14" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="D14" s="4">
+        <v>1.25</v>
+      </c>
+      <c r="E14" s="4">
+        <v>1473</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B15" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="D15" s="5">
+        <v>1.7</v>
+      </c>
+      <c r="E15" s="4">
+        <v>1473</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B16" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="D16" s="5">
+        <v>1.8</v>
+      </c>
+      <c r="E16" s="4">
+        <v>2159</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B17" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="D17" s="5">
+        <v>3</v>
+      </c>
+      <c r="E17" s="4">
+        <v>2159</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B18" s="4">
+        <v>0.8</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="D18" s="5">
+        <v>1.3</v>
+      </c>
+      <c r="E18" s="4">
+        <v>1542</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B19" s="4">
+        <v>0.8</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="D19" s="4">
+        <v>2.15</v>
+      </c>
+      <c r="E19" s="4">
+        <v>1542</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B20" s="4">
+        <v>0.9</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="D20" s="4">
+        <v>1.35</v>
+      </c>
+      <c r="E20" s="4">
+        <v>1614</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B21" s="4">
+        <v>0.9</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="D21" s="4">
+        <v>2.75</v>
+      </c>
+      <c r="E21" s="4">
+        <v>1614</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B22" s="4">
+        <v>1</v>
+      </c>
+      <c r="C22" s="4">
+        <v>1</v>
+      </c>
+      <c r="D22" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="E22" s="4">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B23" s="4">
+        <v>1</v>
+      </c>
+      <c r="C23" s="4">
+        <v>1</v>
+      </c>
+      <c r="D23" s="5">
+        <v>0.9</v>
+      </c>
+      <c r="E23" s="4">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="2">
+        <v>20</v>
+      </c>
+      <c r="B2" s="2">
+        <v>0</v>
+      </c>
+      <c r="C2" s="2">
+        <v>0</v>
+      </c>
+      <c r="D2" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="E2" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="2">
+        <v>20</v>
+      </c>
+      <c r="B3" s="2">
+        <v>0</v>
+      </c>
+      <c r="C3" s="2">
+        <v>0</v>
+      </c>
+      <c r="D3" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="E3" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="2">
+        <v>20</v>
+      </c>
+      <c r="B4" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="C4" s="2">
+        <v>0.101143207694175</v>
+      </c>
+      <c r="D4" s="2">
+        <v>2.2</v>
+      </c>
+      <c r="E4" s="2">
+        <v>2625</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="2">
+        <v>20</v>
+      </c>
+      <c r="B5" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="C5" s="2">
+        <v>0.101143207694175</v>
+      </c>
+      <c r="D5" s="2">
+        <v>2.3</v>
+      </c>
+      <c r="E5" s="2">
+        <v>2625</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="2">
+        <v>20</v>
+      </c>
+      <c r="B6" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="C6" s="2">
+        <v>0.200154924981712</v>
+      </c>
+      <c r="D6" s="2">
+        <v>2.7</v>
+      </c>
+      <c r="E6" s="2">
+        <v>3239</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="2">
+        <v>20</v>
+      </c>
+      <c r="B7" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="C7" s="2">
+        <v>0.200154924981712</v>
+      </c>
+      <c r="D7" s="2">
+        <v>3</v>
+      </c>
+      <c r="E7" s="2">
+        <v>3239</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="2">
+        <v>20</v>
+      </c>
+      <c r="B8" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="C8" s="2">
+        <v>0.299338977674621</v>
+      </c>
+      <c r="D8" s="2">
+        <v>2.45</v>
+      </c>
+      <c r="E8" s="2">
+        <v>2936</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="2">
+        <v>20</v>
+      </c>
+      <c r="B9" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="C9" s="2">
+        <v>0.299338977674621</v>
+      </c>
+      <c r="D9" s="2">
+        <v>2.85</v>
+      </c>
+      <c r="E9" s="2">
+        <v>2936</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="2">
+        <v>20</v>
+      </c>
+      <c r="B10" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="C10" s="2">
+        <v>0.400678189503125</v>
+      </c>
+      <c r="D10" s="2">
+        <v>2</v>
+      </c>
+      <c r="E10" s="2">
+        <v>2387</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="2">
+        <v>20</v>
+      </c>
+      <c r="B11" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="C11" s="2">
+        <v>0.400678189503125</v>
+      </c>
+      <c r="D11" s="2">
+        <v>2.4</v>
+      </c>
+      <c r="E11" s="2">
+        <v>2387</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="2">
+        <v>20</v>
+      </c>
+      <c r="B12" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="C12" s="2">
+        <v>0.499870089058159</v>
+      </c>
+      <c r="D12" s="2">
+        <v>0.15</v>
+      </c>
+      <c r="E12" s="2">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="2">
+        <v>20</v>
+      </c>
+      <c r="B13" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="C13" s="2">
+        <v>0.499870089058159</v>
+      </c>
+      <c r="D13" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="E13" s="2">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="2">
+        <v>20</v>
+      </c>
+      <c r="B14" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="C14" s="2">
+        <v>0.599933246714468</v>
+      </c>
+      <c r="D14" s="2">
+        <v>1.65</v>
+      </c>
+      <c r="E14" s="2">
+        <v>1962</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="2">
+        <v>20</v>
+      </c>
+      <c r="B15" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="C15" s="2">
+        <v>0.599933246714468</v>
+      </c>
+      <c r="D15" s="2">
+        <v>2.15</v>
+      </c>
+      <c r="E15" s="2">
+        <v>1962</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="2">
+        <v>20</v>
+      </c>
+      <c r="B16" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="C16" s="2">
+        <v>0.700221096835872</v>
+      </c>
+      <c r="D16" s="2">
+        <v>1.95</v>
+      </c>
+      <c r="E16" s="2">
+        <v>2336</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="2">
+        <v>20</v>
+      </c>
+      <c r="B17" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="C17" s="2">
+        <v>0.700221096835872</v>
+      </c>
+      <c r="D17" s="2">
+        <v>2.85</v>
+      </c>
+      <c r="E17" s="2">
+        <v>2336</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="2">
+        <v>20</v>
+      </c>
+      <c r="B18" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="C18" s="2">
+        <v>0.800435412423209</v>
+      </c>
+      <c r="D18" s="2">
+        <v>1.05</v>
+      </c>
+      <c r="E18" s="2">
+        <v>1228</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="2">
+        <v>20</v>
+      </c>
+      <c r="B19" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="C19" s="2">
+        <v>0.800435412423209</v>
+      </c>
+      <c r="D19" s="2">
+        <v>1.45</v>
+      </c>
+      <c r="E19" s="2">
+        <v>1228</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="2">
+        <v>20</v>
+      </c>
+      <c r="B20" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="C20" s="2">
+        <v>0.900007855569501</v>
+      </c>
+      <c r="D20" s="2">
+        <v>1.55</v>
+      </c>
+      <c r="E20" s="2">
+        <v>1852</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="2">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="C21" s="2">
+        <v>0.900007855569501</v>
+      </c>
+      <c r="D21" s="2">
+        <v>2.65</v>
+      </c>
+      <c r="E21" s="2">
+        <v>1852</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="2">
+        <v>20</v>
+      </c>
+      <c r="B22" s="2">
+        <v>1</v>
+      </c>
+      <c r="C22" s="2">
+        <v>1</v>
+      </c>
+      <c r="D22" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="E22" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="2">
+        <v>20</v>
+      </c>
+      <c r="B23" s="2">
+        <v>1</v>
+      </c>
+      <c r="C23" s="2">
+        <v>1</v>
+      </c>
+      <c r="D23" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="E23" s="2">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
